--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_s_fonasa_a_2024.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_s_fonasa_a_2024.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:01</t>
+    <t xml:space="preserve">2026-09-24 01:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -790,10 +790,10 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.28</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
@@ -804,10 +804,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
@@ -818,10 +818,10 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -860,10 +860,10 @@
         <v>31</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.12</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25">
@@ -874,10 +874,10 @@
         <v>31</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
@@ -891,7 +891,7 @@
         <v>-0.54</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_s_fonasa_a_2024.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_s_fonasa_a_2024.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:50</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_s_fonasa_a_2024.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_s_fonasa_a_2024.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 20:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
